--- a/PayCalc_V19.xlsx
+++ b/PayCalc_V19.xlsx
@@ -187,7 +187,7 @@
     <t xml:space="preserve">In-charge nights</t>
   </si>
   <si>
-    <t xml:space="preserve">OPS1 on night shift is entitled to the in-charge allowance · $15.65 per shift — rate on Settings &amp; Rates</t>
+    <t xml:space="preserve">OPS1 on night shift is entitled to the in-charge allowance · $16.39 per shift — rate on Settings &amp; Rates</t>
   </si>
   <si>
     <t xml:space="preserve">▸ Paid leave this fortnight</t>
@@ -531,7 +531,7 @@
     <t xml:space="preserve">Leave the payslip column blank when you are not reconciling. A mismatch usually means a rate on Settings &amp; Rates is stale, or payroll treats an allowance differently — see block E for the clause each rate comes from.</t>
   </si>
   <si>
-    <t xml:space="preserve">PayCalc V19 · pay scale award 01.09.2025 · tax tables ATO 01.07.2026 · plain-English guide on the Pay Guide tab · rates, sources &amp; incoming changes on Settings &amp; Rates</t>
+    <t xml:space="preserve">PayCalc V19 · pay scale award 01.09.2026 (current as of 28.10.2026) · tax tables ATO 01.07.2026 · plain-English guide on the Pay Guide tab · rates, sources &amp; incoming changes on Settings &amp; Rates</t>
   </si>
   <si>
     <t xml:space="preserve">PAY  GUIDE</t>
@@ -567,7 +567,7 @@
     <t xml:space="preserve">Award vs EBA</t>
   </si>
   <si>
-    <t xml:space="preserve">You’re paid whichever is better — the agreement can’t pay under the parent award (EBA cl 2.18(6)). Since the 2025 State Wage Case the award rates sit about 1.5% ABOVE the EBA’s final rates, so the award is currently what you’re actually paid.</t>
+    <t xml:space="preserve">You’re paid whichever is better — the agreement can’t pay under the parent award (EBA cl 2.18(6)). Since the 2026 State Wage Case the award rates sit about 6.3% ABOVE the EBA’s final rates, so the award is currently what you’re actually paid.</t>
   </si>
   <si>
     <t xml:space="preserve">②   THE ALLOWANCES — WHAT, HOW MUCH, WHEN</t>
@@ -600,7 +600,7 @@
     <t xml:space="preserve">Laundry</t>
   </si>
   <si>
-    <t xml:space="preserve">$6.10/fn spread across ordinary hours (Award cl 13.6(b)). It is an expense allowance, so it moves with CPI rather than with the State Wage Case (cl 13.7(b)). Only for hours actually worked — no shifts, no washing, no allowance.</t>
+    <t xml:space="preserve">$6.30/fn spread across ordinary hours (Award cl 13.6(b)). It is an expense allowance, so it moves with CPI rather than with the State Wage Case (cl 13.7(b)). Only for hours actually worked — no shifts, no washing, no allowance.</t>
   </si>
   <si>
     <t xml:space="preserve">Qualification</t>
@@ -612,7 +612,7 @@
     <t xml:space="preserve">In-charge</t>
   </si>
   <si>
-    <t xml:space="preserve">$15.65 per shift for the shift supervisor when most of the shift falls outside 0830–1700 — in practice, OPS1 on nights (Award cl 13.2).</t>
+    <t xml:space="preserve">$16.39 per shift for the shift supervisor when most of the shift falls outside 0830–1700 — in practice, OPS1 on nights (Award cl 13.2).</t>
   </si>
   <si>
     <t xml:space="preserve">Other taxable earnings</t>
@@ -756,10 +756,10 @@
     <t xml:space="preserve">Blue-on-yellow cells are the ones you edit. Everything on the calculator reads from here.   |   sheets are protected — password: paycalc  (Review → Unprotect Sheet)</t>
   </si>
   <si>
-    <t xml:space="preserve">A · PAY SCALE — QLD Operational Officers, effective 01.09.2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Source: QIRC 01.09.2025 award reprint (matter B/2025/49-50, incl. 1 Sep 2025 General Ruling). All 15 rows round exactly to the reprint fortnightly $ — see block E</t>
+    <t xml:space="preserve">A · PAY SCALE — QLD Operational Officers, effective 01.09.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source: QIRC 01.09.2026 award reprint (matter B/2026/59-60, incl. 1 Sep 2026 General Ruling, +4.75%; on pay from 28.10.2026). All 15 rows round exactly to the reprint fortnightly $ — see block E</t>
   </si>
   <si>
     <t xml:space="preserve">Permanent $/hr</t>
@@ -810,7 +810,7 @@
     <t xml:space="preserve">L6-3</t>
   </si>
   <si>
-    <t xml:space="preserve">Award rates, effective 01.09.2025 — verified against the QIRC 01.09.2025 award reprint (all 15 rows round exactly to the published fortnightly $). Hourly = fortnightly ÷ 76; casual = permanent × 1.25 (all three columns reconcile exactly). The fortnightly salary is a whole dollar: the 2025 wage case applied 3.5% to the old whole-dollar salary and rounded back to the nearest dollar, e.g. L4-4 $2,993 → $3,097.755 → $3,098 → $40.76316/hr. Cross-checked against a real payslip (11–24 Jul 2026), which pays L4-4 at $40.76316 and L5-1 at $41.78947 — both exact. Keep the rounding when the next wage case lands. The award floor sits above the 01.08.2025 EBA rates and prevails under EBA cl 2.18(6). Custom rates are typed straight on the calculator. Update when the new agreement or the 2026 State Wage Case lands — see block E.</t>
+    <t xml:space="preserve">Award rates, effective 01.09.2026 — verified against the QIRC 01.09.2026 award reprint (all 15 rows round exactly to the published fortnightly $). Hourly = fortnightly ÷ 76; casual = permanent × 1.25 (all three columns reconcile exactly). The fortnightly salary is a whole dollar: each wage case applies its rise to the old whole-dollar salary and rounds back to the nearest dollar — the 2026 case was 4.75%, e.g. L4-4 $3,098 → $3,245.155 → $3,245 → $42.69737/hr. Payroll starts paying these from 28.10.2026, so earlier payslips show the 2025 rates. The rounding was cross-checked against a real payslip at the 2025 rates (11–24 Jul 2026: L4-4 $40.76316, L5-1 $41.78947 — both exact); the 2026 rates haven’t met a payslip yet. Keep the rounding when the next wage case lands. The award floor sits about 6.3% above the 01.08.2025 EBA rates and prevails under EBA cl 2.18(6). Custom rates are typed straight on the calculator. Update when the new agreement or the 2027 State Wage Case lands — see block E.</t>
   </si>
   <si>
     <t xml:space="preserve">B · ALLOWANCE RATES</t>
@@ -867,7 +867,7 @@
     <t xml:space="preserve">EBA cl 2.12 — $45.00/fn ÷ 76, after 2 years' service. Applied to ordinary hours up to 76 — confirmed by a real payslip, where the element is literally named "YD Retent 76" and pays $0.59210/hr on hours worked. Casuals get it pro-rata (EBA cl 2.12(4)). Yes/No toggle lives on the calculator page.</t>
   </si>
   <si>
-    <t xml:space="preserve">Award cl 13.6(b) — $6.10/fn ÷ 76, CPI-adjusted at the 2025 State Wage Case (was $6.00). Set 0 to switch off. (Separate soiled-linen allowance cl 2.11 is out of scope — it applies to OO2 Laundry Assistant / OO3 Laundry Supervisor roles only, not operational shiftworkers.)</t>
+    <t xml:space="preserve">Award cl 13.6(b) — $6.30/fn ÷ 76, CPI-adjusted at the 01.09.2026 reprint (was $6.10). Set 0 to switch off. (Separate soiled-linen allowance cl 2.11 is out of scope — it applies to OO2 Laundry Assistant / OO3 Laundry Supervisor roles only, not operational shiftworkers.)</t>
   </si>
   <si>
     <t xml:space="preserve">$ / night</t>
@@ -969,10 +969,10 @@
     <t xml:space="preserve">Pay scale</t>
   </si>
   <si>
-    <t xml:space="preserve">Award reprint 01.09.2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Youth Detention Centre Employees Award – State 2016, reprinted after the 2025 State Wage Case (3.5%). The award floor now sits above the final EBA rates, and EBA cl 2.18(6) says no one is paid below the parent award — so these are award rates.</t>
+    <t xml:space="preserve">Award reprint 01.09.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Youth Detention Centre Employees Award – State 2016, reprinted after the 2026 State Wage Case (4.75%, matter B/2026/59-60; on pay from 28.10.2026). The award floor now sits about 6.3% above the final EBA rates, and EBA cl 2.18(6) says no one is paid below the parent award — so these are award rates.</t>
   </si>
   <si>
     <t xml:space="preserve">Shift / operational / retention / qualification</t>
@@ -990,7 +990,7 @@
     <t xml:space="preserve">Award cl 13.2 / cl 13.6(b)</t>
   </si>
   <si>
-    <t xml:space="preserve">Award allowances, CPI or wage-case adjusted at each reprint (currently 01.09.2025).</t>
+    <t xml:space="preserve">Award allowances — in-charge moves with the wage case, laundry with CPI (cl 13.7) — adjusted at each reprint (currently 01.09.2026: $16.39/shift, $6.30/fn).</t>
   </si>
   <si>
     <t xml:space="preserve">Directive 16/18</t>
@@ -1023,19 +1023,19 @@
     <t xml:space="preserve">New certified agreement (YDC 2026)</t>
   </si>
   <si>
-    <t xml:space="preserve">OFFER 16.07.2026 — confirmed delayed, not certified</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confirmed delayed (as at 05.08.2026): the department has not responded to the unions’ claims and industrial action is ongoing. Employer Offer dated 16.07.2026 (3-year term, expires 31.07.2029). Three increases: 1 Aug 2026 = 3.5% (3% + 0.5% CPI uplift, already triggered), 1 Aug 2027 = 2.5%, 1 Aug 2028 = 2.5%. The FIRST rise applies to the higher of Award or Agreement — i.e. the Award rate (cl 2.18(6) retained). Allowances that track wages rise by the same %. CONDITIONAL: all unions must agree in-principle by 31.08.2026 to hold the 1 Aug date, else it shifts to the first of the month agreement is reached. NOT applied yet — do not change rates until certified. When certified, the EBA rise builds a SEPARATE agreement ladder — it must NOT be added to block A. Block A is the AWARD ladder; it moves only at a State Wage Case / reprint (~1 Sep). The certification (~1 Aug) and the SWC (~1 Sep) are only 31 days apart, so bumping block A on certification would be overwritten a month later = double-bump. Correct method: 1) build an Agreement-rate column = (award rate at 31.07.2026) × the agreed % for each row; 2) operational rate + $379 cap × same %; 3) set pay = MAX(award, agreement) per row (cl 2.18(6)); 4) block A itself changes ONLY at the SWC/reprint; 5) pull the Rates-checked-until tripwire back to the first-rise date (1 Aug if unions agree by 31 Aug); 6) footer date. Do NOT index: retention (cl 2.12(5) — not subject to annual increase, stays $45.00), shift % (a % of earnings — self-indexes; only change if the certified % changes), qualification (cl 4.2 — no indexation clause, hold pending certified text), in-charge/laundry (move with the award/SWC, not the EBA). YEARS 2-3: each 1 Aug, agreement ladder × 1.025 applied to the PRECEDING AGREEMENT rate (offer wording), NOT the award. After each 1 Sep SWC the award ladder moves independently — keep BOTH ladders live and re-check the MAX winner per row. Caution: if an SWC is ever a flat dollar amount or tiered (not a flat %), the winning ladder can differ by classification — don't assume a blanket MAX. If certification lands after 1 Aug, the first rise backdates and arrives lump-sum-taxed — use the 'Other taxable earnings' row and point to the Pay Guide lump-sum explainer.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">State Wage Case 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">expected 01.09.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Applications are filed with the QIRC. Award minimums and the expense allowances (in-charge, laundry) usually move from 1 September.</t>
+    <t xml:space="preserve">OFFER 16.07.2026 — agreed in principle, not certified</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agreed in principle in late Sep 2026, after months of industrial action; as at 18.10.2026 the agreement is still being written up, then a staff vote and QIRC certification. The terms below are the July offer, not the final deal. Employer Offer dated 16.07.2026 (3-year term, expires 31.07.2029). Three increases: 1 Aug 2026 = 3.5% (3% + 0.5% CPI uplift, already triggered), 1 Aug 2027 = 2.5%, 1 Aug 2028 = 2.5%. The FIRST rise applies to the higher of Award or Agreement — i.e. the Award rate (cl 2.18(6) retained). Allowances that track wages rise by the same %. CONDITIONAL: all unions must agree in-principle by 31.08.2026 to hold the 1 Aug date, else it shifts to the first of the month agreement is reached. NOT applied yet — do not change rates until certified. When certified, the EBA rise builds a SEPARATE agreement ladder — it must NOT be added to block A. Block A is the AWARD ladder; it moves only at a State Wage Case / reprint (~1 Sep). The certification (~1 Aug) and the SWC (~1 Sep) are only 31 days apart, so bumping block A on certification would be overwritten a month later = double-bump. Correct method: 1) build an Agreement-rate column = (award rate at 31.07.2026) × the agreed % for each row; 2) operational rate + $379 cap × same %; 3) set pay = MAX(award, agreement) per row (cl 2.18(6)); 4) block A itself changes ONLY at the SWC/reprint; 5) pull the Rates-checked-until tripwire back to the first-rise date (1 Aug if unions agree by 31 Aug); 6) footer date. Do NOT index: retention (cl 2.12(5) — not subject to annual increase, stays $45.00), shift % (a % of earnings — self-indexes; only change if the certified % changes), qualification (cl 4.2 — no indexation clause, hold pending certified text), in-charge/laundry (move with the award/SWC, not the EBA). YEARS 2-3: each 1 Aug, agreement ladder × 1.025 applied to the PRECEDING AGREEMENT rate (offer wording), NOT the award. After each 1 Sep SWC the award ladder moves independently — keep BOTH ladders live and re-check the MAX winner per row. Caution: if an SWC is ever a flat dollar amount or tiered (not a flat %), the winning ladder can differ by classification — don't assume a blanket MAX. If certification lands after 1 Aug, the first rise backdates and arrives lump-sum-taxed — use the 'Other taxable earnings' row and point to the Pay Guide lump-sum explainer.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">State Wage Case 2027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">expected ~01.09.2027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expected from 1 Sep 2027. Award minimums and the in-charge allowance move by the wage case %; laundry moves by CPI (cl 13.7). The 2026 case (+4.75% from 01.09.2026, on pay from 28.10.2026) is already in block A.</t>
   </si>
   <si>
     <t xml:space="preserve">Tax cut — stage 2</t>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="C6" s="10" t="n">
         <f aca="false">IF(OR($B$6="Custom",$B$6=""),"",IFERROR(INDEX(PayScaleRates,MATCH($B$6,PayScaleNames,0),IF($B$5="Casual",2,1)),""))</f>
-        <v>35.80263</v>
+        <v>37.5</v>
       </c>
       <c r="D6" s="11"/>
       <c r="E6" s="8" t="s">
@@ -2957,7 +2957,7 @@
       </c>
       <c r="C7" s="10" t="n">
         <f aca="false">IF(OR(HDCode="None",HDCode="Custom",HDCode=""),"",IFERROR(INDEX(PayScaleRates,MATCH(HDCode,PayScaleNames,0),IF($B$5="Casual",2,1)),""))</f>
-        <v>41.78947</v>
+        <v>43.77632</v>
       </c>
       <c r="D7" s="11"/>
       <c r="E7" s="8" t="s">
@@ -3485,7 +3485,7 @@
       <c r="E35" s="40"/>
       <c r="F35" s="41" t="n">
         <f aca="false">$J$66-$J$67-$J$68-$J$69-$J$70-$J$71</f>
-        <v>2868.632291296</v>
+        <v>2974.1488200000003</v>
       </c>
       <c r="G35" s="41"/>
       <c r="H35" s="41"/>
@@ -3526,24 +3526,24 @@
     <row r="39" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="44" t="n">
         <f aca="false">$J$58</f>
-        <v>3884.682779296</v>
+        <v>4048.6488200000003</v>
       </c>
       <c r="B39" s="44"/>
       <c r="D39" s="45" t="n">
         <f aca="false">IF((SUM($B$32:$I$32)+LeaveHrs)=0,0,$J$58/(SUM($B$32:$I$32)+LeaveHrs))</f>
-        <v>51.114247096</v>
+        <v>53.271695</v>
       </c>
       <c r="F39" s="45" t="n">
         <f aca="false">IF((SUM($B$32:$I$32)+LeaveHrs)=0,0,NetBank/(SUM($B$32:$I$32)+LeaveHrs))</f>
-        <v>37.7451617275789</v>
+        <v>39.133537105263166</v>
       </c>
       <c r="H39" s="46" t="n">
         <f aca="false">NetBank*FnPerYear</f>
-        <v>74584.439573696</v>
+        <v>77327.86932000001</v>
       </c>
       <c r="J39" s="47" t="n">
         <f aca="false">IF($J$66=0,0,$J$67/$J$66)</f>
-        <v>0.226530723355351</v>
+        <v>0.23020025727990898</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -3571,14 +3571,14 @@
       <c r="D43" s="48"/>
       <c r="F43" s="8" t="str">
         <f aca="false">TEXT($B$32,"0.0")&amp;" hrs × "&amp;TEXT(BaseRate,"$0.00")&amp;IF(LeaveHrs&gt;0,"   +   "&amp;TEXT(LeaveHrs,"0.0")&amp;" leave hrs @ base","")</f>
-        <v>76.0 hrs × $35.80</v>
+        <v>76.0 hrs × $37.50</v>
       </c>
       <c r="G43" s="8"/>
       <c r="H43" s="8"/>
       <c r="I43" s="8"/>
       <c r="J43" s="49" t="n">
         <f aca="false">$B$32*BaseRate+LeavePay</f>
-        <v>2721.00976</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3591,7 +3591,7 @@
       <c r="E44" s="51"/>
       <c r="F44" s="52" t="str">
         <f aca="false">TEXT($C$32,"0.0")&amp;" hrs × "&amp;TEXT(BaseRate*2,"$0.00")</f>
-        <v>0.0 hrs × $71.61</v>
+        <v>0.0 hrs × $75.00</v>
       </c>
       <c r="G44" s="52"/>
       <c r="H44" s="52"/>
@@ -3610,7 +3610,7 @@
       <c r="D45" s="48"/>
       <c r="F45" s="8" t="str">
         <f aca="false">TEXT($D$32,"0.0")&amp;" hrs × "&amp;TEXT(BaseRate*2.5,"$0.00")</f>
-        <v>0.0 hrs × $89.51</v>
+        <v>0.0 hrs × $93.75</v>
       </c>
       <c r="G45" s="8"/>
       <c r="H45" s="8"/>
@@ -3630,7 +3630,7 @@
       <c r="E46" s="51"/>
       <c r="F46" s="52" t="str">
         <f aca="false">TEXT($E$32,"0.0")&amp;" hrs × "&amp;TEXT(BaseRate*4,"$0.00")</f>
-        <v>0.0 hrs × $143.21</v>
+        <v>0.0 hrs × $150.00</v>
       </c>
       <c r="G46" s="52"/>
       <c r="H46" s="52"/>
@@ -3688,7 +3688,7 @@
       <c r="D49" s="54"/>
       <c r="J49" s="55" t="n">
         <f aca="false">SUM(J43:J48)</f>
-        <v>2721.00976</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3708,7 +3708,7 @@
       <c r="I50" s="8"/>
       <c r="J50" s="49" t="n">
         <f aca="false">($B$32*BaseRate+LeavePay*LvShift)*$G$50+$F$32*HDRate*IF(OR(HDCode="None",AND(OR(HDCode="Custom",HDCode=""),N($D$7)=0)),$G$50,IF($B$9="None",0,IF($B$9="OO3-OO5 (26.96%)",Rate_ShiftLo,IF($B$9="OO6 (27.46%)",Rate_ShiftHi,IF(LEFT(HDCode,2)="L6",Rate_ShiftHi,Rate_ShiftLo)))))</f>
-        <v>733.584231296</v>
+        <v>768.36</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3784,7 +3784,7 @@
       <c r="D54" s="48"/>
       <c r="G54" s="58" t="n">
         <f aca="false">Rate_Laun</f>
-        <v>0.080263</v>
+        <v>0.082895</v>
       </c>
       <c r="H54" s="8" t="s">
         <v>76</v>
@@ -3792,7 +3792,7 @@
       <c r="I54" s="8"/>
       <c r="J54" s="49" t="n">
         <f aca="false">MIN($B$32+$F$32+$D$32,76)*$G$54</f>
-        <v>6.099988</v>
+        <v>6.30002</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3834,7 +3834,7 @@
       </c>
       <c r="G56" s="63" t="n">
         <f aca="false">Rate_InCharge</f>
-        <v>15.65</v>
+        <v>16.39</v>
       </c>
       <c r="H56" s="8" t="s">
         <v>83</v>
@@ -3854,7 +3854,7 @@
       <c r="D57" s="54"/>
       <c r="J57" s="55" t="n">
         <f aca="false">SUM(J50:J56)+CustomAllow</f>
-        <v>1163.673019296</v>
+        <v>1198.6488200000001</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3871,7 +3871,7 @@
       <c r="I58" s="65"/>
       <c r="J58" s="66" t="n">
         <f aca="false">J49+J57</f>
-        <v>3884.682779296</v>
+        <v>4048.6488200000003</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4018,7 +4018,7 @@
       <c r="D66" s="67"/>
       <c r="J66" s="68" t="n">
         <f aca="false">$J$58-SUM($J$62:$J$65)</f>
-        <v>3884.682779296</v>
+        <v>4048.6488200000003</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4037,7 +4037,7 @@
       <c r="I67" s="8"/>
       <c r="J67" s="69" t="n">
         <f aca="false">PAYG_FN</f>
-        <v>880</v>
+        <v>932</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4080,7 +4080,7 @@
       <c r="I69" s="8"/>
       <c r="J69" s="49" t="n">
         <f aca="false">IF($E$62="No — after-tax",$E$69*($J$43+$F$32*HDRate+$D$32*BaseRate),0)</f>
-        <v>136.050488</v>
+        <v>142.5</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4159,7 +4159,7 @@
       <c r="I73" s="8"/>
       <c r="J73" s="49" t="n">
         <f aca="false">EmpSuperRate*($J$43+$J$45+$J$48+$F$32*HDRate+$J$57-CustomAllow)</f>
-        <v>494.51930589024</v>
+        <v>516.2027245500001</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4198,7 +4198,7 @@
       <c r="I75" s="8"/>
       <c r="J75" s="49" t="n">
         <f aca="false">$J$69</f>
-        <v>136.050488</v>
+        <v>142.5</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4210,7 +4210,7 @@
       <c r="D76" s="67"/>
       <c r="J76" s="68" t="n">
         <f aca="false">SUM(J73:J75)</f>
-        <v>630.56979389024</v>
+        <v>658.7027245500001</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4228,7 +4228,7 @@
       <c r="I77" s="8"/>
       <c r="J77" s="72" t="n">
         <f aca="false">($J$73+$J$74)*FnPerYear</f>
-        <v>12857.5019531462</v>
+        <v>13421.270838300003</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4265,7 +4265,7 @@
       <c r="I79" s="8"/>
       <c r="J79" s="72" t="n">
         <f aca="false">$J$78-$J$77</f>
-        <v>19642.4980468538</v>
+        <v>19078.729161699997</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4284,7 +4284,7 @@
       <c r="I80" s="52"/>
       <c r="J80" s="74" t="n">
         <f aca="false">MAX(0,$J$79/FnPerYear)</f>
-        <v>755.48069410976</v>
+        <v>733.7972754499999</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -4326,12 +4326,12 @@
       <c r="D84" s="22"/>
       <c r="F84" s="77" t="n">
         <f aca="false">IF($J$58=0,0,J84/$J$58)</f>
-        <v>0.738446986349775</v>
+        <v>0.7346028149707488</v>
       </c>
       <c r="G84" s="77"/>
       <c r="J84" s="24" t="n">
         <f aca="false">NetBank</f>
-        <v>2868.632291296</v>
+        <v>2974.1488200000003</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4344,14 +4344,14 @@
       <c r="E85" s="51"/>
       <c r="F85" s="79" t="n">
         <f aca="false">IF($J$58=0,0,J85/$J$58)</f>
-        <v>0.226530723355351</v>
+        <v>0.23020025727990898</v>
       </c>
       <c r="G85" s="79"/>
       <c r="H85" s="51"/>
       <c r="I85" s="51"/>
       <c r="J85" s="80" t="n">
         <f aca="false">$J$67</f>
-        <v>880</v>
+        <v>932</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4400,12 +4400,12 @@
       <c r="D88" s="22"/>
       <c r="F88" s="77" t="n">
         <f aca="false">IF($J$58=0,0,J88/$J$58)</f>
-        <v>0.0350222902948734</v>
+        <v>0.035196927749342306</v>
       </c>
       <c r="G88" s="77"/>
       <c r="J88" s="24" t="n">
         <f aca="false">$J$69</f>
-        <v>136.050488</v>
+        <v>142.5</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4473,7 +4473,7 @@
       <c r="E93" s="62"/>
       <c r="F93" s="24" t="n">
         <f aca="false">$J$58</f>
-        <v>3884.682779296</v>
+        <v>4048.6488200000003</v>
       </c>
       <c r="G93" s="24"/>
       <c r="H93" s="82" t="str">
@@ -4496,7 +4496,7 @@
       <c r="E94" s="62"/>
       <c r="F94" s="80" t="n">
         <f aca="false">$J$67</f>
-        <v>880</v>
+        <v>932</v>
       </c>
       <c r="G94" s="80"/>
       <c r="H94" s="84" t="str">
@@ -4519,7 +4519,7 @@
       <c r="E95" s="62"/>
       <c r="F95" s="24" t="n">
         <f aca="false">NetBank</f>
-        <v>2868.632291296</v>
+        <v>2974.1488200000003</v>
       </c>
       <c r="G95" s="24"/>
       <c r="H95" s="82" t="str">
@@ -4542,7 +4542,7 @@
       <c r="E96" s="62"/>
       <c r="F96" s="80" t="n">
         <f aca="false">$J$73</f>
-        <v>494.51930589024</v>
+        <v>516.2027245500001</v>
       </c>
       <c r="G96" s="80"/>
       <c r="H96" s="84" t="str">
@@ -4820,7 +4820,7 @@
       <formula1>"Yes,No"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" prompt="Nights you were in charge of shift (OPS1 on nights). $15.65 per night, award cl 13.2." promptTitle="In-charge nights" showDropDown="false" showErrorMessage="false" showInputMessage="true" sqref="B13" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" prompt="Nights you were in charge of shift (OPS1 on nights). $16.39 per night, award cl 13.2." promptTitle="In-charge nights" showDropDown="false" showErrorMessage="false" showInputMessage="true" sqref="B13" type="list">
       <formula1>"1,2,3,4,5,6,7,8,9,10,11,12,13,14"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -5725,15 +5725,15 @@
         <v>218</v>
       </c>
       <c r="B6" s="96" t="n">
-        <v>33.71053</v>
+        <v>35.31579</v>
       </c>
       <c r="C6" s="97" t="n">
         <f aca="false">B6*1.25</f>
-        <v>42.1381625</v>
+        <v>44.1447375</v>
       </c>
       <c r="D6" s="98" t="n">
         <f aca="false">B6*76</f>
-        <v>2562</v>
+        <v>2684.00004</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5741,15 +5741,15 @@
         <v>219</v>
       </c>
       <c r="B7" s="96" t="n">
-        <v>34.35526</v>
+        <v>35.98684</v>
       </c>
       <c r="C7" s="97" t="n">
         <f aca="false">B7*1.25</f>
-        <v>42.944075</v>
+        <v>44.98355</v>
       </c>
       <c r="D7" s="98" t="n">
         <f aca="false">B7*76</f>
-        <v>2611</v>
+        <v>2734.99984</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5757,15 +5757,15 @@
         <v>220</v>
       </c>
       <c r="B8" s="96" t="n">
-        <v>35.07895</v>
+        <v>36.75</v>
       </c>
       <c r="C8" s="97" t="n">
         <f aca="false">B8*1.25</f>
-        <v>43.8486875</v>
+        <v>45.9375</v>
       </c>
       <c r="D8" s="98" t="n">
         <f aca="false">B8*76</f>
-        <v>2666</v>
+        <v>2793</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5773,15 +5773,15 @@
         <v>7</v>
       </c>
       <c r="B9" s="96" t="n">
-        <v>35.80263</v>
+        <v>37.5</v>
       </c>
       <c r="C9" s="97" t="n">
         <f aca="false">B9*1.25</f>
-        <v>44.7532875</v>
+        <v>46.875</v>
       </c>
       <c r="D9" s="98" t="n">
         <f aca="false">B9*76</f>
-        <v>2721</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5789,15 +5789,15 @@
         <v>221</v>
       </c>
       <c r="B10" s="96" t="n">
-        <v>37.25</v>
+        <v>39.01316</v>
       </c>
       <c r="C10" s="97" t="n">
         <f aca="false">B10*1.25</f>
-        <v>46.5625</v>
+        <v>48.76645</v>
       </c>
       <c r="D10" s="98" t="n">
         <f aca="false">B10*76</f>
-        <v>2831</v>
+        <v>2965.00016</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5805,15 +5805,15 @@
         <v>222</v>
       </c>
       <c r="B11" s="96" t="n">
-        <v>38.42105</v>
+        <v>40.25</v>
       </c>
       <c r="C11" s="97" t="n">
         <f aca="false">B11*1.25</f>
-        <v>48.0263125</v>
+        <v>50.3125</v>
       </c>
       <c r="D11" s="98" t="n">
         <f aca="false">B11*76</f>
-        <v>2920</v>
+        <v>3059</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5821,15 +5821,15 @@
         <v>223</v>
       </c>
       <c r="B12" s="96" t="n">
-        <v>39.61842</v>
+        <v>41.5</v>
       </c>
       <c r="C12" s="97" t="n">
         <f aca="false">B12*1.25</f>
-        <v>49.523025</v>
+        <v>51.875</v>
       </c>
       <c r="D12" s="98" t="n">
         <f aca="false">B12*76</f>
-        <v>3011</v>
+        <v>3154</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5837,15 +5837,15 @@
         <v>224</v>
       </c>
       <c r="B13" s="96" t="n">
-        <v>40.76316</v>
+        <v>42.69737</v>
       </c>
       <c r="C13" s="97" t="n">
         <f aca="false">B13*1.25</f>
-        <v>50.95395</v>
+        <v>53.3717125</v>
       </c>
       <c r="D13" s="98" t="n">
         <f aca="false">B13*76</f>
-        <v>3098</v>
+        <v>3245.00012</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5853,15 +5853,15 @@
         <v>10</v>
       </c>
       <c r="B14" s="96" t="n">
-        <v>41.78947</v>
+        <v>43.77632</v>
       </c>
       <c r="C14" s="97" t="n">
         <f aca="false">B14*1.25</f>
-        <v>52.2368375</v>
+        <v>54.7204</v>
       </c>
       <c r="D14" s="98" t="n">
         <f aca="false">B14*76</f>
-        <v>3176</v>
+        <v>3327.00032</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5869,15 +5869,15 @@
         <v>225</v>
       </c>
       <c r="B15" s="96" t="n">
-        <v>43.10526</v>
+        <v>45.15789</v>
       </c>
       <c r="C15" s="97" t="n">
         <f aca="false">B15*1.25</f>
-        <v>53.881575</v>
+        <v>56.447362500000004</v>
       </c>
       <c r="D15" s="98" t="n">
         <f aca="false">B15*76</f>
-        <v>3276</v>
+        <v>3431.99964</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5885,15 +5885,15 @@
         <v>226</v>
       </c>
       <c r="B16" s="96" t="n">
-        <v>44.48684</v>
+        <v>46.60526</v>
       </c>
       <c r="C16" s="97" t="n">
         <f aca="false">B16*1.25</f>
-        <v>55.60855</v>
+        <v>58.256575</v>
       </c>
       <c r="D16" s="98" t="n">
         <f aca="false">B16*76</f>
-        <v>3381</v>
+        <v>3541.99976</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5901,15 +5901,15 @@
         <v>227</v>
       </c>
       <c r="B17" s="96" t="n">
-        <v>45.82895</v>
+        <v>48.0</v>
       </c>
       <c r="C17" s="97" t="n">
         <f aca="false">B17*1.25</f>
-        <v>57.2861875</v>
+        <v>60</v>
       </c>
       <c r="D17" s="98" t="n">
         <f aca="false">B17*76</f>
-        <v>3483</v>
+        <v>3648</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5917,15 +5917,15 @@
         <v>228</v>
       </c>
       <c r="B18" s="96" t="n">
-        <v>47.76316</v>
+        <v>50.02632</v>
       </c>
       <c r="C18" s="97" t="n">
         <f aca="false">B18*1.25</f>
-        <v>59.70395</v>
+        <v>62.5329</v>
       </c>
       <c r="D18" s="98" t="n">
         <f aca="false">B18*76</f>
-        <v>3630</v>
+        <v>3802.00032</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5933,15 +5933,15 @@
         <v>229</v>
       </c>
       <c r="B19" s="96" t="n">
-        <v>49.02632</v>
+        <v>51.35526</v>
       </c>
       <c r="C19" s="97" t="n">
         <f aca="false">B19*1.25</f>
-        <v>61.2829</v>
+        <v>64.194075</v>
       </c>
       <c r="D19" s="98" t="n">
         <f aca="false">B19*76</f>
-        <v>3726</v>
+        <v>3902.99976</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5949,15 +5949,15 @@
         <v>230</v>
       </c>
       <c r="B20" s="96" t="n">
-        <v>50.22368</v>
+        <v>52.60526</v>
       </c>
       <c r="C20" s="97" t="n">
         <f aca="false">B20*1.25</f>
-        <v>62.7796</v>
+        <v>65.756575</v>
       </c>
       <c r="D20" s="98" t="n">
         <f aca="false">B20*76</f>
-        <v>3817</v>
+        <v>3997.99976</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6078,7 +6078,7 @@
         <v>160</v>
       </c>
       <c r="B31" s="96" t="n">
-        <v>0.080263</v>
+        <v>0.082895</v>
       </c>
       <c r="C31" s="100" t="s">
         <v>243</v>
@@ -6092,7 +6092,7 @@
         <v>164</v>
       </c>
       <c r="B32" s="62" t="n">
-        <v>15.65</v>
+        <v>16.39</v>
       </c>
       <c r="C32" s="100" t="s">
         <v>251</v>
@@ -6256,7 +6256,7 @@
         <v>277</v>
       </c>
       <c r="B49" s="104" t="n">
-        <v>46266</v>
+        <v>46631</v>
       </c>
       <c r="F49" s="99" t="s">
         <v>278</v>
@@ -6478,15 +6478,15 @@
       </c>
       <c r="B70" s="96">
         <f aca="false">(ROUND(D9,0)+$B$36)/76</f>
-        <v>36.34868421052632</v>
+        <v>38.046052631578945</v>
       </c>
       <c r="C70" s="97">
         <f aca="false">B70*1.25</f>
-        <v>45.4358552631579</v>
+        <v>47.557565789473685</v>
       </c>
       <c r="D70" s="98">
         <f aca="false">B70*76</f>
-        <v>2762.5</v>
+        <v>2891.5</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6497,15 +6497,15 @@
       </c>
       <c r="B71" s="96">
         <f aca="false">(ROUND(D13,0)+$B$37)/76</f>
-        <v>41.32631578947368</v>
+        <v>43.26052631578948</v>
       </c>
       <c r="C71" s="97">
         <f aca="false">B71*1.25</f>
-        <v>51.65789473684211</v>
+        <v>54.07565789473685</v>
       </c>
       <c r="D71" s="98">
         <f aca="false">B71*76</f>
-        <v>3140.8</v>
+        <v>3287.8</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6516,15 +6516,15 @@
       </c>
       <c r="B72" s="96">
         <f aca="false">(ROUND(D17,0)+$B$37)/76</f>
-        <v>46.3921052631579</v>
+        <v>48.56315789473685</v>
       </c>
       <c r="C72" s="97">
         <f aca="false">B72*1.25</f>
-        <v>57.99013157894737</v>
+        <v>60.703947368421055</v>
       </c>
       <c r="D72" s="98">
         <f aca="false">B72*76</f>
-        <v>3525.8</v>
+        <v>3690.8</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6535,15 +6535,15 @@
       </c>
       <c r="B73" s="96">
         <f aca="false">(ROUND(D20,0)+$B$38)/76</f>
-        <v>50.81052631578947</v>
+        <v>53.19210526315789</v>
       </c>
       <c r="C73" s="97">
         <f aca="false">B73*1.25</f>
-        <v>63.51315789473684</v>
+        <v>66.49013157894737</v>
       </c>
       <c r="D73" s="98">
         <f aca="false">B73*76</f>
-        <v>3861.6</v>
+        <v>4042.6</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6653,14 +6653,14 @@
       </c>
       <c r="B5" s="110" t="n">
         <f aca="false">'Pay Calculator'!$J$66</f>
-        <v>3884.682779296</v>
+        <v>4048.6488200000003</v>
       </c>
       <c r="E5" s="111" t="s">
         <v>322</v>
       </c>
       <c r="F5" s="112" t="n">
         <f aca="false">IF(OR('Pay Calculator'!$B$6="Custom",'Pay Calculator'!$B$6=""),N('Pay Calculator'!$D$6),IFERROR(INDEX(QScaleRates,MATCH('Pay Calculator'!$B$6,QScaleNames,0),IF('Pay Calculator'!$B$5="Casual",2,1)),IFERROR(INDEX(PayScaleRates,MATCH('Pay Calculator'!$B$6,PayScaleNames,0),IF('Pay Calculator'!$B$5="Casual",2,1)),N('Pay Calculator'!$D$6))))</f>
-        <v>35.80263</v>
+        <v>37.5</v>
       </c>
       <c r="H5" s="111" t="s">
         <v>323</v>
@@ -6676,14 +6676,14 @@
       </c>
       <c r="B6" s="115" t="n">
         <f aca="false">TRUNC(MAX(0,B5)/2,0)</f>
-        <v>1942</v>
+        <v>2024</v>
       </c>
       <c r="E6" s="111" t="s">
         <v>325</v>
       </c>
       <c r="F6" s="112" t="n">
         <f aca="false">IF(HDCode="None",F5,IF(OR(HDCode="Custom",HDCode=""),IF(N('Pay Calculator'!$D$7)&gt;0,N('Pay Calculator'!$D$7),F5),IFERROR(INDEX(PayScaleRates,MATCH(HDCode,PayScaleNames,0),IF('Pay Calculator'!$B$5="Casual",2,1)),N('Pay Calculator'!$D$7))))</f>
-        <v>41.78947</v>
+        <v>43.77632</v>
       </c>
       <c r="H6" s="111" t="s">
         <v>326</v>
@@ -6699,7 +6699,7 @@
       </c>
       <c r="B7" s="117" t="n">
         <f aca="false">B6+0.99</f>
-        <v>1942.99</v>
+        <v>2024.99</v>
       </c>
       <c r="E7" s="111" t="s">
         <v>328</v>
@@ -6760,7 +6760,7 @@
       </c>
       <c r="F10" s="120" t="n">
         <f aca="false">ROUND($B$7*C10-D10,0)*2</f>
-        <v>1100</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6777,7 +6777,7 @@
       </c>
       <c r="F11" s="120" t="n">
         <f aca="false">ROUND($B$7*C11-D11,0)*2</f>
-        <v>880</v>
+        <v>932</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6794,7 +6794,7 @@
       </c>
       <c r="F12" s="120" t="n">
         <f aca="false">ROUND($B$7*C12-D12,0)*2</f>
-        <v>1166</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="F13" s="120" t="n">
         <f aca="false">ROUND($B$7*C13-D13,0)*2</f>
-        <v>802</v>
+        <v>852</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6828,7 +6828,7 @@
       </c>
       <c r="F14" s="120" t="n">
         <f aca="false">ROUND($B$7*C14-D14,0)*2</f>
-        <v>842</v>
+        <v>892</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6841,7 +6841,7 @@
       </c>
       <c r="F15" s="122" t="n">
         <f aca="false">INDEX($F$10:$F$14,MATCH(ScaleUsed,$A$10:$A$14,0))</f>
-        <v>880</v>
+        <v>932</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6850,7 +6850,7 @@
       </c>
       <c r="F17" s="120" t="n">
         <f aca="false">ROUND($B$7*VLOOKUP($B$6,LU_Scale_HELP_TFTR,2)-VLOOKUP($B$6,LU_Scale_HELP_TFTR,3),0)*2</f>
-        <v>182</v>
+        <v>206</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6859,7 +6859,7 @@
       </c>
       <c r="F18" s="120" t="n">
         <f aca="false">ROUND($B$7*VLOOKUP($B$6,LU_Scale_HELP_NTFT,2)-VLOOKUP($B$6,LU_Scale_HELP_NTFT,3),0)*2</f>
-        <v>286</v>
+        <v>312</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6910,15 +6910,15 @@
       </c>
       <c r="C24" s="123" t="n">
         <f aca="false">BaseRate*(1+'Pay Calculator'!$G$50)+IF('Pay Calculator'!$B$32&lt;76,('Pay Calculator'!$G$51+'Pay Calculator'!$G$52+'Pay Calculator'!$G$53+'Pay Calculator'!$G$54),0)</f>
-        <v>45.455184096</v>
+        <v>47.61</v>
       </c>
       <c r="D24" s="123" t="n">
         <f aca="false">BaseRate*2</f>
-        <v>71.60552</v>
+        <v>75</v>
       </c>
       <c r="E24" s="123" t="n">
         <f aca="false">BaseRate*2.5</f>
-        <v>89.5069</v>
+        <v>93.75</v>
       </c>
       <c r="F24" s="123" t="s">
         <v>352</v>
@@ -6950,23 +6950,23 @@
       </c>
       <c r="B26" s="123" t="n">
         <f aca="false">MAX(0,$B$5+B24-B25)</f>
-        <v>3884.682779296</v>
+        <v>4048.6488200000003</v>
       </c>
       <c r="C26" s="123" t="n">
         <f aca="false">MAX(0,$B$5+C24-C25)</f>
-        <v>3930.137963392</v>
+        <v>4096.25882</v>
       </c>
       <c r="D26" s="123" t="n">
         <f aca="false">MAX(0,$B$5+D24-D25)</f>
-        <v>3956.288299296</v>
+        <v>4123.64882</v>
       </c>
       <c r="E26" s="123" t="n">
         <f aca="false">MAX(0,$B$5+E24-E25)</f>
-        <v>3974.189679296</v>
+        <v>4142.39882</v>
       </c>
       <c r="F26" s="123" t="n">
         <f aca="false">MAX(0,$B$5+F24-F25)</f>
-        <v>3784.682779296</v>
+        <v>3948.6488200000003</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6975,23 +6975,23 @@
       </c>
       <c r="B27" s="124" t="n">
         <f aca="false">TRUNC(B26/2,0)</f>
-        <v>1942</v>
+        <v>2024</v>
       </c>
       <c r="C27" s="124" t="n">
         <f aca="false">TRUNC(C26/2,0)</f>
-        <v>1965</v>
+        <v>2048</v>
       </c>
       <c r="D27" s="124" t="n">
         <f aca="false">TRUNC(D26/2,0)</f>
-        <v>1978</v>
+        <v>2061</v>
       </c>
       <c r="E27" s="124" t="n">
         <f aca="false">TRUNC(E26/2,0)</f>
-        <v>1987</v>
+        <v>2071</v>
       </c>
       <c r="F27" s="124" t="n">
         <f aca="false">TRUNC(F26/2,0)</f>
-        <v>1892</v>
+        <v>1974</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7000,23 +7000,23 @@
       </c>
       <c r="B28" s="125" t="n">
         <f aca="false">B27+0.99</f>
-        <v>1942.99</v>
+        <v>2024.99</v>
       </c>
       <c r="C28" s="125" t="n">
         <f aca="false">C27+0.99</f>
-        <v>1965.99</v>
+        <v>2048.99</v>
       </c>
       <c r="D28" s="125" t="n">
         <f aca="false">D27+0.99</f>
-        <v>1978.99</v>
+        <v>2061.99</v>
       </c>
       <c r="E28" s="125" t="n">
         <f aca="false">E27+0.99</f>
-        <v>1987.99</v>
+        <v>2071.99</v>
       </c>
       <c r="F28" s="125" t="n">
         <f aca="false">F27+0.99</f>
-        <v>1892.99</v>
+        <v>1974.99</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7025,23 +7025,23 @@
       </c>
       <c r="B30" s="127" t="n">
         <f aca="false">ROUND(B$28*VLOOKUP(B$27,LU_Scale1,2)-VLOOKUP(B$27,LU_Scale1,3),0)*2</f>
-        <v>1100</v>
+        <v>1152</v>
       </c>
       <c r="C30" s="127" t="n">
         <f aca="false">ROUND(C$28*VLOOKUP(C$27,LU_Scale1,2)-VLOOKUP(C$27,LU_Scale1,3),0)*2</f>
-        <v>1114</v>
+        <v>1168</v>
       </c>
       <c r="D30" s="127" t="n">
         <f aca="false">ROUND(D$28*VLOOKUP(D$27,LU_Scale1,2)-VLOOKUP(D$27,LU_Scale1,3),0)*2</f>
-        <v>1124</v>
+        <v>1176</v>
       </c>
       <c r="E30" s="127" t="n">
         <f aca="false">ROUND(E$28*VLOOKUP(E$27,LU_Scale1,2)-VLOOKUP(E$27,LU_Scale1,3),0)*2</f>
-        <v>1130</v>
+        <v>1182</v>
       </c>
       <c r="F30" s="127" t="n">
         <f aca="false">ROUND(F$28*VLOOKUP(F$27,LU_Scale1,2)-VLOOKUP(F$27,LU_Scale1,3),0)*2</f>
-        <v>1068</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7050,23 +7050,23 @@
       </c>
       <c r="B31" s="127" t="n">
         <f aca="false">ROUND(B$28*VLOOKUP(B$27,LU_Scale2,2)-VLOOKUP(B$27,LU_Scale2,3),0)*2</f>
-        <v>880</v>
+        <v>932</v>
       </c>
       <c r="C31" s="127" t="n">
         <f aca="false">ROUND(C$28*VLOOKUP(C$27,LU_Scale2,2)-VLOOKUP(C$27,LU_Scale2,3),0)*2</f>
-        <v>894</v>
+        <v>948</v>
       </c>
       <c r="D31" s="127" t="n">
         <f aca="false">ROUND(D$28*VLOOKUP(D$27,LU_Scale2,2)-VLOOKUP(D$27,LU_Scale2,3),0)*2</f>
-        <v>904</v>
+        <v>956</v>
       </c>
       <c r="E31" s="127" t="n">
         <f aca="false">ROUND(E$28*VLOOKUP(E$27,LU_Scale2,2)-VLOOKUP(E$27,LU_Scale2,3),0)*2</f>
-        <v>908</v>
+        <v>962</v>
       </c>
       <c r="F31" s="127" t="n">
         <f aca="false">ROUND(F$28*VLOOKUP(F$27,LU_Scale2,2)-VLOOKUP(F$27,LU_Scale2,3),0)*2</f>
-        <v>848</v>
+        <v>900</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7075,23 +7075,23 @@
       </c>
       <c r="B32" s="127" t="n">
         <f aca="false">ROUND(B$28*VLOOKUP(B$27,LU_Scale3,2)-VLOOKUP(B$27,LU_Scale3,3),0)*2</f>
-        <v>1166</v>
+        <v>1214</v>
       </c>
       <c r="C32" s="127" t="n">
         <f aca="false">ROUND(C$28*VLOOKUP(C$27,LU_Scale3,2)-VLOOKUP(C$27,LU_Scale3,3),0)*2</f>
-        <v>1178</v>
+        <v>1228</v>
       </c>
       <c r="D32" s="127" t="n">
         <f aca="false">ROUND(D$28*VLOOKUP(D$27,LU_Scale3,2)-VLOOKUP(D$27,LU_Scale3,3),0)*2</f>
-        <v>1186</v>
+        <v>1236</v>
       </c>
       <c r="E32" s="127" t="n">
         <f aca="false">ROUND(E$28*VLOOKUP(E$27,LU_Scale3,2)-VLOOKUP(E$27,LU_Scale3,3),0)*2</f>
-        <v>1192</v>
+        <v>1242</v>
       </c>
       <c r="F32" s="127" t="n">
         <f aca="false">ROUND(F$28*VLOOKUP(F$27,LU_Scale3,2)-VLOOKUP(F$27,LU_Scale3,3),0)*2</f>
-        <v>1136</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7100,23 +7100,23 @@
       </c>
       <c r="B33" s="127" t="n">
         <f aca="false">ROUND(B$28*VLOOKUP(B$27,LU_Scale5,2)-VLOOKUP(B$27,LU_Scale5,3),0)*2</f>
-        <v>802</v>
+        <v>852</v>
       </c>
       <c r="C33" s="127" t="n">
         <f aca="false">ROUND(C$28*VLOOKUP(C$27,LU_Scale5,2)-VLOOKUP(C$27,LU_Scale5,3),0)*2</f>
-        <v>816</v>
+        <v>866</v>
       </c>
       <c r="D33" s="127" t="n">
         <f aca="false">ROUND(D$28*VLOOKUP(D$27,LU_Scale5,2)-VLOOKUP(D$27,LU_Scale5,3),0)*2</f>
-        <v>824</v>
+        <v>874</v>
       </c>
       <c r="E33" s="127" t="n">
         <f aca="false">ROUND(E$28*VLOOKUP(E$27,LU_Scale5,2)-VLOOKUP(E$27,LU_Scale5,3),0)*2</f>
-        <v>830</v>
+        <v>880</v>
       </c>
       <c r="F33" s="127" t="n">
         <f aca="false">ROUND(F$28*VLOOKUP(F$27,LU_Scale5,2)-VLOOKUP(F$27,LU_Scale5,3),0)*2</f>
-        <v>772</v>
+        <v>822</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7125,23 +7125,23 @@
       </c>
       <c r="B34" s="127" t="n">
         <f aca="false">ROUND(B$28*VLOOKUP(B$27,LU_Scale6,2)-VLOOKUP(B$27,LU_Scale6,3),0)*2</f>
-        <v>842</v>
+        <v>892</v>
       </c>
       <c r="C34" s="127" t="n">
         <f aca="false">ROUND(C$28*VLOOKUP(C$27,LU_Scale6,2)-VLOOKUP(C$27,LU_Scale6,3),0)*2</f>
-        <v>856</v>
+        <v>906</v>
       </c>
       <c r="D34" s="127" t="n">
         <f aca="false">ROUND(D$28*VLOOKUP(D$27,LU_Scale6,2)-VLOOKUP(D$27,LU_Scale6,3),0)*2</f>
-        <v>864</v>
+        <v>914</v>
       </c>
       <c r="E34" s="127" t="n">
         <f aca="false">ROUND(E$28*VLOOKUP(E$27,LU_Scale6,2)-VLOOKUP(E$27,LU_Scale6,3),0)*2</f>
-        <v>870</v>
+        <v>922</v>
       </c>
       <c r="F34" s="127" t="n">
         <f aca="false">ROUND(F$28*VLOOKUP(F$27,LU_Scale6,2)-VLOOKUP(F$27,LU_Scale6,3),0)*2</f>
-        <v>810</v>
+        <v>862</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7150,23 +7150,23 @@
       </c>
       <c r="B35" s="120" t="n">
         <f aca="false">INDEX(B30:B34,MATCH(ScaleUsed,$A$10:$A$14,0))</f>
-        <v>880</v>
+        <v>932</v>
       </c>
       <c r="C35" s="120" t="n">
         <f aca="false">INDEX(C30:C34,MATCH(ScaleUsed,$A$10:$A$14,0))</f>
-        <v>894</v>
+        <v>948</v>
       </c>
       <c r="D35" s="120" t="n">
         <f aca="false">INDEX(D30:D34,MATCH(ScaleUsed,$A$10:$A$14,0))</f>
-        <v>904</v>
+        <v>956</v>
       </c>
       <c r="E35" s="120" t="n">
         <f aca="false">INDEX(E30:E34,MATCH(ScaleUsed,$A$10:$A$14,0))</f>
-        <v>908</v>
+        <v>962</v>
       </c>
       <c r="F35" s="120" t="n">
         <f aca="false">INDEX(F30:F34,MATCH(ScaleUsed,$A$10:$A$14,0))</f>
-        <v>848</v>
+        <v>900</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7175,23 +7175,23 @@
       </c>
       <c r="B36" s="127" t="n">
         <f aca="false">ROUND(B$28*VLOOKUP(B$27,LU_Scale_HELP_TFTR,2)-VLOOKUP(B$27,LU_Scale_HELP_TFTR,3),0)*2</f>
-        <v>182</v>
+        <v>206</v>
       </c>
       <c r="C36" s="127" t="n">
         <f aca="false">ROUND(C$28*VLOOKUP(C$27,LU_Scale_HELP_TFTR,2)-VLOOKUP(C$27,LU_Scale_HELP_TFTR,3),0)*2</f>
-        <v>188</v>
+        <v>214</v>
       </c>
       <c r="D36" s="127" t="n">
         <f aca="false">ROUND(D$28*VLOOKUP(D$27,LU_Scale_HELP_TFTR,2)-VLOOKUP(D$27,LU_Scale_HELP_TFTR,3),0)*2</f>
-        <v>192</v>
+        <v>218</v>
       </c>
       <c r="E36" s="127" t="n">
         <f aca="false">ROUND(E$28*VLOOKUP(E$27,LU_Scale_HELP_TFTR,2)-VLOOKUP(E$27,LU_Scale_HELP_TFTR,3),0)*2</f>
-        <v>196</v>
+        <v>220</v>
       </c>
       <c r="F36" s="127" t="n">
         <f aca="false">ROUND(F$28*VLOOKUP(F$27,LU_Scale_HELP_TFTR,2)-VLOOKUP(F$27,LU_Scale_HELP_TFTR,3),0)*2</f>
-        <v>166</v>
+        <v>192</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7200,23 +7200,23 @@
       </c>
       <c r="B37" s="127" t="n">
         <f aca="false">ROUND(B$28*VLOOKUP(B$27,LU_Scale_HELP_NTFT,2)-VLOOKUP(B$27,LU_Scale_HELP_NTFT,3),0)*2</f>
-        <v>286</v>
+        <v>312</v>
       </c>
       <c r="C37" s="127" t="n">
         <f aca="false">ROUND(C$28*VLOOKUP(C$27,LU_Scale_HELP_NTFT,2)-VLOOKUP(C$27,LU_Scale_HELP_NTFT,3),0)*2</f>
-        <v>294</v>
+        <v>318</v>
       </c>
       <c r="D37" s="127" t="n">
         <f aca="false">ROUND(D$28*VLOOKUP(D$27,LU_Scale_HELP_NTFT,2)-VLOOKUP(D$27,LU_Scale_HELP_NTFT,3),0)*2</f>
-        <v>298</v>
+        <v>322</v>
       </c>
       <c r="E37" s="127" t="n">
         <f aca="false">ROUND(E$28*VLOOKUP(E$27,LU_Scale_HELP_NTFT,2)-VLOOKUP(E$27,LU_Scale_HELP_NTFT,3),0)*2</f>
-        <v>300</v>
+        <v>326</v>
       </c>
       <c r="F37" s="127" t="n">
         <f aca="false">ROUND(F$28*VLOOKUP(F$27,LU_Scale_HELP_NTFT,2)-VLOOKUP(F$27,LU_Scale_HELP_NTFT,3),0)*2</f>
-        <v>272</v>
+        <v>296</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7253,7 +7253,7 @@
       </c>
       <c r="C39" s="123" t="n">
         <f aca="false">MemberPct*BaseRate</f>
-        <v>1.790138</v>
+        <v>1.875</v>
       </c>
       <c r="D39" s="123" t="n">
         <v>0</v>
@@ -7275,15 +7275,15 @@
       </c>
       <c r="C40" s="129" t="n">
         <f aca="false">(C26-$B$26)-(C35-$B$35)-(C38-$B$38)-C39</f>
-        <v>29.6650460959998</v>
+        <v>29.734999999999673</v>
       </c>
       <c r="D40" s="129" t="n">
         <f aca="false">(D26-$B$26)-(D35-$B$35)-(D38-$B$38)-D39</f>
-        <v>47.6055200000001</v>
+        <v>51</v>
       </c>
       <c r="E40" s="129" t="n">
         <f aca="false">(E26-$B$26)-(E35-$B$35)-(E38-$B$38)-E39</f>
-        <v>61.5068999999999</v>
+        <v>63.75</v>
       </c>
       <c r="F40" s="129" t="n">
         <f aca="false">(F26-$B$26)-(F35-$B$35)-(F38-$B$38)-F39</f>
